--- a/config/data/BattleParticipantSlot.xlsx
+++ b/config/data/BattleParticipantSlot.xlsx
@@ -1,136 +1,91 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="BattleParticipantSlot" sheetId="1" r:id="rId1"/>
+    <sheet name="BattleParticipantSlot" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="31">
-  <si>
-    <t>@table</t>
-  </si>
-  <si>
-    <t>BattleParticipantSlot</t>
-  </si>
-  <si>
-    <t>@mode</t>
-  </si>
-  <si>
-    <t>list</t>
-  </si>
-  <si>
-    <t>@key</t>
-  </si>
-  <si>
-    <t>@scope</t>
-  </si>
-  <si>
-    <t>all</t>
-  </si>
-  <si>
-    <t>@schema</t>
-  </si>
-  <si>
-    <t>33c37e3f3c9c7e2d</t>
-  </si>
-  <si>
-    <t>#name</t>
-  </si>
-  <si>
-    <t>battle_binding_id</t>
-  </si>
-  <si>
-    <t>team_index</t>
-  </si>
-  <si>
-    <t>formation_index</t>
-  </si>
-  <si>
-    <t>character_id</t>
-  </si>
-  <si>
-    <t>resolved_spec_sha256</t>
-  </si>
-  <si>
-    <t>build_digest_sha256</t>
-  </si>
-  <si>
-    <t>build_catalog_revision</t>
-  </si>
-  <si>
-    <t>source_kind</t>
-  </si>
-  <si>
-    <t>#field</t>
-  </si>
-  <si>
-    <t>#type</t>
-  </si>
-  <si>
-    <t>ref&lt;BattleBinding.id&gt;</t>
-  </si>
-  <si>
-    <t>i32</t>
-  </si>
-  <si>
-    <t>ref&lt;Character.id&gt;</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>enum&lt;ParticipantSourceKind&gt;</t>
-  </si>
-  <si>
-    <t>#scope</t>
-  </si>
-  <si>
-    <t>#input</t>
-  </si>
-  <si>
-    <t>range=0..7</t>
-  </si>
-  <si>
-    <t>length=64..64</t>
-  </si>
-  <si>
-    <t>length=1..80</t>
-  </si>
-  <si>
-    <t>#desc</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <numFmts count="0"/>
+  <fonts count="3">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FF1F2937"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="8">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2F3A4A"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9EEF5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3D6E8F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDE5EF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6F8FB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF7DB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -138,18 +93,118 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  <cellXfs count="7">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -437,181 +492,1141 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12.7109375" customWidth="1" min="1" max="1"/>
+    <col width="21.7109375" customWidth="1" style="5" min="2" max="2"/>
+    <col width="12.7109375" customWidth="1" style="5" min="3" max="3"/>
+    <col width="15.7109375" customWidth="1" style="5" min="4" max="4"/>
+    <col width="23.7109375" customWidth="1" style="5" min="5" max="5"/>
+    <col width="20.7109375" customWidth="1" style="5" min="6" max="6"/>
+    <col width="19.7109375" customWidth="1" style="5" min="7" max="7"/>
+    <col width="22.7109375" customWidth="1" style="5" min="8" max="8"/>
+    <col width="27.7109375" customWidth="1" style="5" min="9" max="9"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>@table</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>BattleParticipantSlot</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>@mode</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>list</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>@key</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>@scope</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>@schema</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>3921c64303047b69</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>#name</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>battle_binding_id</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>team_index</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>formation_index</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>character_id</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>resolved_spec_sha256</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>build_digest_sha256</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>build_catalog_revision</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>source_kind</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>#field</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>battle_binding_id</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>team_index</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>formation_index</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>character_id</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>resolved_spec_sha256</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>build_digest_sha256</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>build_catalog_revision</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>source_kind</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>#type</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>ref&lt;BattleBinding.id&gt;</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>i32</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>i32</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>ref&lt;ContentIdentity.id&gt;</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>enum&lt;ParticipantSourceKind&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>#scope</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>#input</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>range=0..7</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>range=0..7</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>length=64..64</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>length=64..64</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>length=1..80</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="n"/>
+    </row>
+    <row r="7" ht="42" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>#desc</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n"/>
+      <c r="C7" s="6" t="n"/>
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="n"/>
+      <c r="H7" s="6" t="n"/>
+      <c r="I7" s="6" t="n"/>
+    </row>
+    <row r="8">
+      <c r="B8" t="n">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>8</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>8d5060b04e8428b6b5473765d13b925f7e74fe93dcb7bca5fdd72c9f301c095f</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>f80e924aec625d8da6a3f689b62c6d27d3d4ca90eb54896541638353cd5afee4</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>core-combat-v1-standard-lock-v1</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>CompiledBuild</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="n">
+        <v>20</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>ee9d5b5fc7255b3b32932b40a363e36c1683a70d2b3a13630cb1878de401f90f</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>6c4e50106b672578bf7822762c33ac106fbdad19175e24e99d28f84cc68f1fd5</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>core-combat-v1-standard-lock-v1</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>CompiledBuild</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E10" t="n">
+        <v>50</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>1feb0af0ba76cb3564127af5cc888ceb5bf42b28a2a999ac79dbf4a7bcf7a3d8</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>c3cb98f6b44182f76286c14d873cf7264d17c8b8ffcece5fbccbfa97726e6f0c</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>core-combat-v1-standard-lock-v1</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>CompiledBuild</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E11" t="n">
+        <v>56</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>f8aa1b56c50b3653dc626bcc39f9e6c3a33719c8799b13b78d83db225b50970a</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>9bf44d41a0d47d7332ab30329716debf55128f27d59886f45554bdf5ae814f81</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>core-combat-v1-standard-lock-v1</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>CompiledBuild</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="n">
+        <v>2</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>45</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>d3ae8fc125f315bbae5403ab5ffc94a46159a1d38eca13acbfa2828788261898</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>23f974a203825424afe4b3f6bcf62296316a3224181673fd25bae3eb7d3572a8</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>core-combat-v1-standard-lock-v1</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>CompiledBuild</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="n">
+        <v>2</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" t="n">
+        <v>64</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>fa44ea5bf95c2afdf8543b207de124cfd74a90bbf75511a00c91d2d52134b98e</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>135d6e408d724c0a50185d8ec68bee2ebc5dd0e76ad443c39c8a9a230d28e4cd</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>core-combat-v1-standard-lock-v1</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>CompiledBuild</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="n">
+        <v>2</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E14" t="n">
+        <v>8</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>3d43c6f8a446677b3edef7ad91687f78f80a564300adf4fe48d80d87a2705aba</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>904f956908e2d3bcf8c2004e669a9c5950382c149d31ae401d03dc5d629c85d3</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>core-combat-v1-standard-lock-v1</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>CompiledBuild</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="n">
+        <v>2</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E15" t="n">
+        <v>10</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>3ade846823f90766dee559c4292bf8749af837d3bd7ab2d1696dac32cc448440</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>26f0b674f23351e9189300069c17e17be9b896420e4ece79907f591526a76a64</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>core-combat-v1-standard-lock-v1</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>CompiledBuild</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="n">
+        <v>3</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>18</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>c11035afed08b857a04e88ca3d36c3ab06596f82ac159bdf9bf392a808094db5</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>b31e161e0f1a606898d380331fbb5c5e8f759c4095d99ae5b9d3deb7578f4065</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>core-combat-v1-standard-lock-v1</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>CompiledBuild</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="n">
+        <v>3</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" t="n">
+        <v>75</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>571fc8fee55be81537ba85c0454a9e8604858e151e2c0d6d0948a56be7fe520d</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>ddb5a3fe27cb00d0ed3c18f49df63474ae1ff2d3dda37fbbbb279821cf547442</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>core-combat-v1-standard-lock-v1</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>CompiledBuild</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="n">
+        <v>3</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E18" t="n">
+        <v>50</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>fc613adbdfae5244572920bc00a92adbc22aec22ef02f1937991de7b1be1d42f</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>8951cbc84324faf83b25501428387bb5676d793af3a1af1acdbf72d1b32baf17</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>core-combat-v1-standard-lock-v1</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>CompiledBuild</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="n">
+        <v>3</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" t="n">
+        <v>3</v>
+      </c>
+      <c r="E19" t="n">
+        <v>49</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>a0d9f5ea751658aad984dbbf4c612824d16fc32970dbe96ef63daddb98a3fc87</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>ab8ab0fc81cc098fb48363faddb954d5582184d3029a08123d5fccba467652a2</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>core-combat-v1-standard-lock-v1</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>CompiledBuild</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="n">
         <v>4</v>
       </c>
-      <c r="G1" t="s">
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>27</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>835d8eb9c579ccbb9682367db864613f29ec70d09d50c0226bf7eaa2163d3c5b</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>04b8aed67e72dea4f3f9fec66bd9ae0a179ce7764239ff691de185b0623290ef</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>core-combat-v1-standard-lock-v1</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>CompiledBuild</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="n">
+        <v>4</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" t="n">
+        <v>62</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>bf1a45925eeeaa743355bd269d258b990e9f5f6cab1eb36eaa21d29672bffdfd</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>66a65b558cb9ebf019353e15c389804a69f63b54754834622a856bee56ca1b64</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>core-combat-v1-standard-lock-v1</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>CompiledBuild</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="n">
+        <v>4</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2</v>
+      </c>
+      <c r="E22" t="n">
+        <v>79</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>37c248434529716f95ccafdd6041311d2e62f1cb3f84c99454ddb5d700d98e0a</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>cdd521df219940e4c8cc8366c8e876df0edc3e673e725fa7df731419230bcaf5</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>core-combat-v1-standard-lock-v1</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>CompiledBuild</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="n">
+        <v>4</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" t="n">
+        <v>3</v>
+      </c>
+      <c r="E23" t="n">
+        <v>30</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>b0da33d4dd21abd1bcd903ec06987492fcda81a392876091485d3fee79aa1fc4</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>a3a1441f8e176ea5f06fbe63262922e4f1f8b4519d9999cd3818d584489a7daa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>core-combat-v1-standard-lock-v1</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>CompiledBuild</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="n">
         <v>5</v>
       </c>
-      <c r="H1" t="s">
+      <c r="C24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="n">
+        <v>27</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>aaa2acd6299558ffebb6990f149fc02afa43f7581c7d4d7fcbc9c04a8d8b82f2</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>adedaec847876f5c285d857e3a06291d6a5fce05ddd4ae067f952d8cac2a84e4</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>core-combat-v1-standard-lock-v1</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>CompiledBuild</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="n">
+        <v>5</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" t="n">
+        <v>29</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>bae7eaa4c8a942db9e01e97759c8de632157d160c4ef61c7dc12401ea1461299</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>37a05eef9cba797fb6739e5ec864aa98121607c79e1d13b92b28c33aea10c4f2</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>core-combat-v1-standard-lock-v1</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>CompiledBuild</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="n">
+        <v>5</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" t="n">
+        <v>2</v>
+      </c>
+      <c r="E26" t="n">
+        <v>62</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>9dcf60a1bd5b9f36df91a17bd5551ad4af98842f034e956ec7d11046ebbbfef7</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>ce20bfbe495e213ba7c5a99cce7599a70de8a3caaf4f2453a3cc862e352f0393</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>core-combat-v1-standard-lock-v1</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>CompiledBuild</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="n">
+        <v>5</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" t="n">
+        <v>3</v>
+      </c>
+      <c r="E27" t="n">
+        <v>30</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>1008b4605dc59fef4fc5d8d81e6970b63eba734c7a8c74ec8e730e334b824b78</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>052cfa883dd6152d68f207bc49cb471b22ee008095cd5a1d86f6197dbc9a3687</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>core-combat-v1-standard-lock-v1</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>CompiledBuild</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="n">
         <v>6</v>
       </c>
-      <c r="I1" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" t="s">
+      <c r="C28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" t="n">
+        <v>34</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>4763166908ed0f028ae1c06e7e631efe66534b63ba800c45ab2ec4e2a76905a4</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>28c2565f7d623303f65524d35688d179632c09b36651a442d174576f13093ce4</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>core-combat-v1-standard-lock-v1</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>CompiledBuild</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="n">
+        <v>6</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" t="n">
+        <v>35</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>12493244c0b4a719902be2aecb7e03f73666d48457f73215b56fcba0811bce19</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>7be734f4b49e860df9d1f57a7d39cd48570ae88497583a86211cccaa665c3e85</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>core-combat-v1-standard-lock-v1</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>CompiledBuild</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="n">
+        <v>6</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" t="n">
+        <v>2</v>
+      </c>
+      <c r="E30" t="n">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>58f577cbe4d542ee544651f85bd98e7d275cfb3453bb0852076d4eff27aeb912</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>310d08e9904ff50743b524f67032f6c8de52b3512ec4277a4a3300d63576099e</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>core-combat-v1-standard-lock-v1</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>CompiledBuild</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="n">
+        <v>6</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" t="n">
+        <v>3</v>
+      </c>
+      <c r="E31" t="n">
         <v>10</v>
       </c>
-      <c r="C2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3" t="s">
-        <v>15</v>
-      </c>
-      <c r="H3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F4" t="s">
-        <v>23</v>
-      </c>
-      <c r="G4" t="s">
-        <v>23</v>
-      </c>
-      <c r="H4" t="s">
-        <v>23</v>
-      </c>
-      <c r="I4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" t="s">
-        <v>25</v>
-      </c>
-      <c r="B5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E5" t="s">
-        <v>6</v>
-      </c>
-      <c r="F5" t="s">
-        <v>6</v>
-      </c>
-      <c r="G5" t="s">
-        <v>6</v>
-      </c>
-      <c r="H5" t="s">
-        <v>6</v>
-      </c>
-      <c r="I5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C6" t="s">
-        <v>27</v>
-      </c>
-      <c r="D6" t="s">
-        <v>27</v>
-      </c>
-      <c r="F6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G6" t="s">
-        <v>28</v>
-      </c>
-      <c r="H6" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" t="s">
-        <v>30</v>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>641af1c45a128d462231678ca4412d2f92621ae8680a069e4b4831deb3889dfe</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>51582a1b3b289b6bd3c11767b6b505033b915abab34e0dc59d473aacff22603e</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>core-combat-v1-standard-lock-v1</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>CompiledBuild</t>
+        </is>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="3">
+    <dataValidation sqref="C8:C1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 0 to 7." promptTitle="Integer range" prompt="Enter an integer from 0 to 7." type="whole">
+      <formula1>0</formula1>
+      <formula2>7</formula2>
+    </dataValidation>
+    <dataValidation sqref="D8:D1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 0 to 7." promptTitle="Integer range" prompt="Enter an integer from 0 to 7." type="whole">
+      <formula1>0</formula1>
+      <formula2>7</formula2>
+    </dataValidation>
+    <dataValidation sqref="I8:I1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: CompiledBuild, FixedResolved, Trial, Synthetic" promptTitle="ParticipantSourceKind enum" prompt="Select a value from the dropdown." type="list">
+      <formula1>"CompiledBuild,FixedResolved,Trial,Synthetic"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>